--- a/www/download/IND.labour_force_value.s.mv.rpPE.xlsx
+++ b/www/download/IND.labour_force_value.s.mv.rpPE.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>65336.917</t>
+          <t>65336916566.009</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>71851.62</t>
+          <t>71851620078.593</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>73188.082</t>
+          <t>73188081826.291</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69817.49</t>
+          <t>69817489743.2766</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>74755.074</t>
+          <t>74755074250.9876</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>75061.419</t>
+          <t>75061418527.6929</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>72056.85</t>
+          <t>72056849764.6633</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77794.165</t>
+          <t>77794164623.5488</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>86217.996</t>
+          <t>86217996075.9169</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>101319.025</t>
+          <t>101319025046.298</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>105239.188</t>
+          <t>105239187923.182</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>105474.051</t>
+          <t>105474050609.47</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>107059.959</t>
+          <t>107059959281.154</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>105015.577</t>
+          <t>105015576550.515</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>108296.916</t>
+          <t>108296915991.675</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>44044.247</t>
+          <t>44044246795.0373</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>41360.636</t>
+          <t>41360635761.4869</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>37549.623</t>
+          <t>37549622923.0877</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>40727.778</t>
+          <t>40727777601.6486</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>39987.774</t>
+          <t>39987774384.0306</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>37487.939</t>
+          <t>37487938804.0718</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>38113.123</t>
+          <t>38113123114.2932</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>39882.931</t>
+          <t>39882931447.6634</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>42293.968</t>
+          <t>42293967616.9449</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>45771.558</t>
+          <t>45771557740.7418</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>44103.79</t>
+          <t>44103789963.9765</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>43250.831</t>
+          <t>43250831067.6193</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>41768.751</t>
+          <t>41768750891.9083</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>42023.891</t>
+          <t>42023890859.9408</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>42192.195</t>
+          <t>42192195454.7032</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>50167.889</t>
+          <t>50167889314.2036</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>47383.684</t>
+          <t>47383684273.4539</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>43923.715</t>
+          <t>43923715269.6767</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>47555.487</t>
+          <t>47555487280.0519</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>47484.974</t>
+          <t>47484973729.6408</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>45063.719</t>
+          <t>45063718763.834</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>47480.146</t>
+          <t>47480145508.1477</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>50725.492</t>
+          <t>50725491719.7482</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>53629.246</t>
+          <t>53629246339.1724</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>58480.661</t>
+          <t>58480661026.216</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>56218.221</t>
+          <t>56218220916.0115</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>55123.371</t>
+          <t>55123371413.057</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>53289.907</t>
+          <t>53289907078.2163</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>53435.975</t>
+          <t>53435975175.8477</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>54133.539</t>
+          <t>54133539392.488</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1889.017</t>
+          <t>1889016940.49712</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1681.556</t>
+          <t>1681555674.74844</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1307.222</t>
+          <t>1307221984.37031</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1812.492</t>
+          <t>1812491641.65091</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1741.982</t>
+          <t>1741982082.14773</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1664.067</t>
+          <t>1664066595.52367</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1860.142</t>
+          <t>1860142307.96881</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2032.153</t>
+          <t>2032152904.17513</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2300.104</t>
+          <t>2300104207.66578</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2635.303</t>
+          <t>2635302866.92844</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2691.932</t>
+          <t>2691932340.84715</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2794.714</t>
+          <t>2794714244.4879</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>3101.013</t>
+          <t>3101013018.97584</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>3563.957</t>
+          <t>3563957026.47218</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>3794.122</t>
+          <t>3794121822.76224</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>112877.918</t>
+          <t>112877917632.869</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>119914.709</t>
+          <t>119914709414.728</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>124241.961</t>
+          <t>124241961059.752</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>129899.426</t>
+          <t>129899426467.217</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>88243.758</t>
+          <t>88243757639.0835</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>99241.961</t>
+          <t>99241961239.4429</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>88488.088</t>
+          <t>88488087599.7542</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>79247.525</t>
+          <t>79247525051.8118</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>72620.071</t>
+          <t>72620070738.4204</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>83386.063</t>
+          <t>83386062961.9126</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>105354.71</t>
+          <t>105354710055.548</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>122674.311</t>
+          <t>122674310675.909</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>130896.101</t>
+          <t>130896101194.137</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>142040.723</t>
+          <t>142040722730.031</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>153469.421</t>
+          <t>153469420697.304</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>105003.215</t>
+          <t>105003214781.701</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>105604.233</t>
+          <t>105604232610.502</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>113118.724</t>
+          <t>113118724053.986</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>117679.576</t>
+          <t>117679575649.689</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>122975.107</t>
+          <t>122975106587.479</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>139673.723</t>
+          <t>139673722515.866</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>144120.732</t>
+          <t>144120731738.297</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>144300.922</t>
+          <t>144300921759.818</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>147234.657</t>
+          <t>147234657484.412</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>161721.155</t>
+          <t>161721154667.588</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>170550.436</t>
+          <t>170550435691.631</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>180542.029</t>
+          <t>180542029437.895</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>168986.684</t>
+          <t>168986683619.634</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>160277.753</t>
+          <t>160277753487.718</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>150249.142</t>
+          <t>150249141673.557</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>136908.933</t>
+          <t>136908932642.724</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>157085.334</t>
+          <t>157085333752.36</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>178110.151</t>
+          <t>178110151107.911</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>198855.79</t>
+          <t>198855789517.711</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>204703.043</t>
+          <t>204703043354.539</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>230931.035</t>
+          <t>230931035040.162</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>257615.219</t>
+          <t>257615219322.18</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>269449.593</t>
+          <t>269449592884.157</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>256883.754</t>
+          <t>256883754317.016</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>287173.338</t>
+          <t>287173337878.094</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>302080.707</t>
+          <t>302080706579.394</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>325438.796</t>
+          <t>325438796041.856</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>340316.194</t>
+          <t>340316193618.095</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>391556.358</t>
+          <t>391556358154.505</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>453413.351</t>
+          <t>453413350864.812</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1379.668</t>
+          <t>1379667722.88091</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1380.545</t>
+          <t>1380545262.37383</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1376.116</t>
+          <t>1376115854.5808</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1524.836</t>
+          <t>1524835610.94901</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1534.477</t>
+          <t>1534477477.83965</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1511.117</t>
+          <t>1511116727.54682</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1600.865</t>
+          <t>1600865286.35889</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1776.704</t>
+          <t>1776703716.9046</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2014.68</t>
+          <t>2014680164.67523</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2276.546</t>
+          <t>2276546056.31934</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2265.995</t>
+          <t>2265994999.01491</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2269.966</t>
+          <t>2269965680.39367</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2211.777</t>
+          <t>2211777468.53703</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2265.157</t>
+          <t>2265156933.77188</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2302.876</t>
+          <t>2302875609.81806</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6270.022</t>
+          <t>6270021667.49311</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9130.695</t>
+          <t>9130694732.43547</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8724.997</t>
+          <t>8724997142.35975</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>9576.115</t>
+          <t>9576114549.92573</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9135.34</t>
+          <t>9135340345.81533</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>9073.37</t>
+          <t>9073370481.51882</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10230.25</t>
+          <t>10230249879.7631</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>12442.595</t>
+          <t>12442595341.5407</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>13251.718</t>
+          <t>13251717830.2902</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>14955.747</t>
+          <t>14955746962.3705</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>15923.69</t>
+          <t>15923690122.5392</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>16916.421</t>
+          <t>16916420948.4119</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>17374.014</t>
+          <t>17374014157.6259</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>19673.044</t>
+          <t>19673043605.6188</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>18026.205</t>
+          <t>18026204807.9823</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>469118.536</t>
+          <t>469118536131.935</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>440001.412</t>
+          <t>440001411764.606</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>394676.878</t>
+          <t>394676878267.554</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>421666.338</t>
+          <t>421666337607.901</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>410478.38</t>
+          <t>410478380402.276</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>386526.298</t>
+          <t>386526298304.309</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>392892.435</t>
+          <t>392892435374.633</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>406858.676</t>
+          <t>406858676255.024</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>423711.348</t>
+          <t>423711347602.265</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>451567.291</t>
+          <t>451567290650.952</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>417287.638</t>
+          <t>417287638412.232</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>397420.235</t>
+          <t>397420234697.836</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>374845.127</t>
+          <t>374845126901.064</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>371747.535</t>
+          <t>371747535100.686</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>376715.345</t>
+          <t>376715345244.607</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>32681.26</t>
+          <t>32681259925.3423</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>32452.62</t>
+          <t>32452620465.6517</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>30754.454</t>
+          <t>30754454444.6717</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>34068.944</t>
+          <t>34068944414.6591</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>33984.839</t>
+          <t>33984838560.7144</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>32066.833</t>
+          <t>32066832772.4966</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>33700.672</t>
+          <t>33700672364.9197</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>35949.486</t>
+          <t>35949486206.6818</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>38327.256</t>
+          <t>38327255791.7583</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>41873.095</t>
+          <t>41873095474.4178</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>40808.012</t>
+          <t>40808011977.6094</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>40371.011</t>
+          <t>40371011416.5733</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>39610.541</t>
+          <t>39610541492.3347</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>39623.624</t>
+          <t>39623623696.0581</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>40037.712</t>
+          <t>40037711601.431</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>100416.11</t>
+          <t>100416110182.299</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>102477.915</t>
+          <t>102477915445.054</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>98293.433</t>
+          <t>98293433029.858</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>109217.226</t>
+          <t>109217226049.822</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>111212.259</t>
+          <t>111212258773.234</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>109529.469</t>
+          <t>109529468772.638</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>117181.877</t>
+          <t>117181877175.018</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>127956.569</t>
+          <t>127956569133.445</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>141550.335</t>
+          <t>141550334630.424</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>159189.783</t>
+          <t>159189783187.352</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>158979.933</t>
+          <t>158979933352.72</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>160569.126</t>
+          <t>160569125827.037</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>159473.119</t>
+          <t>159473119489.44</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>160924.618</t>
+          <t>160924617914.909</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>157894.669</t>
+          <t>157894669061.949</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>680.725</t>
+          <t>680725456.213121</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>793.336</t>
+          <t>793335698.369706</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>843.435</t>
+          <t>843435123.453234</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>976.709</t>
+          <t>976708691.175692</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>961.362</t>
+          <t>961361569.847542</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>978.534</t>
+          <t>978534007.968294</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1083.461</t>
+          <t>1083460862.9687</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1237.41</t>
+          <t>1237410106.26732</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1443.24</t>
+          <t>1443240425.13201</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1702.593</t>
+          <t>1702593495.65543</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1824.426</t>
+          <t>1824426072.26712</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2053.398</t>
+          <t>2053397944.56365</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2339.787</t>
+          <t>2339786671.79483</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2529.038</t>
+          <t>2529038155.68554</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2239.479</t>
+          <t>2239478995.36791</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>22291.932</t>
+          <t>22291931950.2133</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>21533.641</t>
+          <t>21533640537.423</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20661.893</t>
+          <t>20661893128.0207</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>22909.777</t>
+          <t>22909776541.5921</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22726.883</t>
+          <t>22726883343.5788</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>21888.281</t>
+          <t>21888280693.3805</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>23267.486</t>
+          <t>23267486008.7183</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>24653.703</t>
+          <t>24653703107.3779</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>26336.459</t>
+          <t>26336458705.8515</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>29091.778</t>
+          <t>29091777897.6455</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>28465.184</t>
+          <t>28465183776.0969</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>27872.888</t>
+          <t>27872887853.7435</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>27136.172</t>
+          <t>27136171760.6727</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>27526.432</t>
+          <t>27526432458.3721</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>27436.172</t>
+          <t>27436171723.5529</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>280259.433</t>
+          <t>280259432582.105</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>274143.04</t>
+          <t>274143040175.552</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>253719.972</t>
+          <t>253719971736.188</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>276482.861</t>
+          <t>276482861311.547</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>274274.556</t>
+          <t>274274556093.711</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>262329.561</t>
+          <t>262329560980.797</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>273614.491</t>
+          <t>273614491204.499</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>293103.494</t>
+          <t>293103493735.914</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>313151.991</t>
+          <t>313151991095.036</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>343968.075</t>
+          <t>343968075239.964</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>331483.965</t>
+          <t>331483965447.249</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>323843.968</t>
+          <t>323843968106.896</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>309390.846</t>
+          <t>309390846291.93</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>305244.939</t>
+          <t>305244938732.233</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>305741.127</t>
+          <t>305741127176.241</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>209685.665</t>
+          <t>209685664995.484</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>211841.477</t>
+          <t>211841476799.599</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>243151.257</t>
+          <t>243151256719.959</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>282966.58</t>
+          <t>282966580071.692</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>291266.386</t>
+          <t>291266385708.144</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>306503.871</t>
+          <t>306503870937.08</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>317585.35</t>
+          <t>317585349793.599</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>335888.017</t>
+          <t>335888016836.554</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>333269.729</t>
+          <t>333269728624.845</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>379147.545</t>
+          <t>379147544723.346</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>369652.984</t>
+          <t>369652984053.602</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>365340.213</t>
+          <t>365340213447.899</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>352274.758</t>
+          <t>352274758401.441</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>295781.897</t>
+          <t>295781897430.161</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>265566.16</t>
+          <t>265566159612.699</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14457.433</t>
+          <t>14457432978.9497</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>14765.601</t>
+          <t>14765601361.6919</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>15226.128</t>
+          <t>15226127584.8932</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>16481.168</t>
+          <t>16481167747.6969</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>17150.587</t>
+          <t>17150587181.0961</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>16110.568</t>
+          <t>16110567883.9404</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>16760.537</t>
+          <t>16760537091.1741</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>19942.978</t>
+          <t>19942978493.461</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>22430.584</t>
+          <t>22430584337.3537</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>25738.234</t>
+          <t>25738234182.905</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>25311.649</t>
+          <t>25311648592.5919</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>25518.11</t>
+          <t>25518109555.6234</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>25529.522</t>
+          <t>25529522008.1592</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>26183.119</t>
+          <t>26183118649.886</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>27191.755</t>
+          <t>27191755381.1413</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>7277.628</t>
+          <t>7277627710.3639</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6986.884</t>
+          <t>6986884303.18098</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7215.871</t>
+          <t>7215871109.92938</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7834.671</t>
+          <t>7834671466.55288</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>7639.212</t>
+          <t>7639212426.59064</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7940.944</t>
+          <t>7940943819.15723</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>9329.498</t>
+          <t>9329497664.52703</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>11553.234</t>
+          <t>11553233930.7535</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>12802.184</t>
+          <t>12802184039.1012</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>14984.337</t>
+          <t>14984337229.5081</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>15277.761</t>
+          <t>15277760664.9153</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>14341.459</t>
+          <t>14341459083.3561</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>14791.526</t>
+          <t>14791525577.8826</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>14765.054</t>
+          <t>14765053997.3726</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>12746.334</t>
+          <t>12746333519.3651</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>25700.67</t>
+          <t>25700670076.3761</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>28805.248</t>
+          <t>28805247555.846</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>29512.125</t>
+          <t>29512124984.2727</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>11865.499</t>
+          <t>11865499437.0748</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>17804.779</t>
+          <t>17804778853.6656</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>19818.441</t>
+          <t>19818441474.8942</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>19986.498</t>
+          <t>19986498183.5786</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>23628.151</t>
+          <t>23628150509.3881</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>24680.205</t>
+          <t>24680205272.3263</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>25167.936</t>
+          <t>25167936145.0292</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>25527.362</t>
+          <t>25527362460.2279</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>31600.134</t>
+          <t>31600134160.5982</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>31391.276</t>
+          <t>31391275515.4665</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>32824.782</t>
+          <t>32824781672.9009</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>37021.098</t>
+          <t>37021098480.5786</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>42537.477</t>
+          <t>42537477147.0731</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>40318.135</t>
+          <t>40318135260.9091</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>48115.209</t>
+          <t>48115209093.0485</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>51223.384</t>
+          <t>51223384435.6255</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>53031.623</t>
+          <t>53031623197.2766</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>56409.314</t>
+          <t>56409313574.785</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>59659.315</t>
+          <t>59659315348.1878</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>60066.604</t>
+          <t>60066604250.62</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>60314.923</t>
+          <t>60314922756.6474</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>67128.328</t>
+          <t>67128328496.0511</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>72709.534</t>
+          <t>72709534354.5374</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>75096.751</t>
+          <t>75096750504.1823</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>78182.767</t>
+          <t>78182766967.1801</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>75713.883</t>
+          <t>75713883017.91</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>83935.701</t>
+          <t>83935700624.7757</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>10398.08</t>
+          <t>10398080037.8985</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>11035.516</t>
+          <t>11035515540.1474</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>11992.733</t>
+          <t>11992732990.1798</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>13535.385</t>
+          <t>13535384995.9475</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>14242.378</t>
+          <t>14242377697.6444</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>14692.813</t>
+          <t>14692812566.3511</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>16335.538</t>
+          <t>16335538102.9978</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>18014.414</t>
+          <t>18014414254.6636</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>20215.437</t>
+          <t>20215437002.522</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>23355.567</t>
+          <t>23355567030.3484</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>24375.006</t>
+          <t>24375006148.1122</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>25132.981</t>
+          <t>25132980798.7213</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>25008.825</t>
+          <t>25008824791.7567</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>25418.747</t>
+          <t>25418746821.0492</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>23223.698</t>
+          <t>23223697692.3098</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>160131.489</t>
+          <t>160131488584.315</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>175140.812</t>
+          <t>175140812339.871</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>171377.66</t>
+          <t>171377659828.374</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>177197.572</t>
+          <t>177197572495.566</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>173479.862</t>
+          <t>173479862053.002</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>163988.533</t>
+          <t>163988533082.37</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>172703.991</t>
+          <t>172703991329.755</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>185854.49</t>
+          <t>185854490208.457</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>200505.451</t>
+          <t>200505450676.256</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>220461.848</t>
+          <t>220461847536.569</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>214760.029</t>
+          <t>214760028604.981</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>210451.315</t>
+          <t>210451315192.19</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>200906.619</t>
+          <t>200906618557.442</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>198853.052</t>
+          <t>198853051507.741</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>198263.969</t>
+          <t>198263969081.39</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>944737.105</t>
+          <t>944737104536.676</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>791397.753</t>
+          <t>791397752940.208</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>744220.689</t>
+          <t>744220688684.43</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>721233.991</t>
+          <t>721233990850.369</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>801281.524</t>
+          <t>801281523516.931</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>894816.496</t>
+          <t>894816495982.734</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>809197.646</t>
+          <t>809197646071.101</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>745382.044</t>
+          <t>745382043559.537</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>691744.425</t>
+          <t>691744425404.328</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>725180.647</t>
+          <t>725180646902.837</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>667383.504</t>
+          <t>667383503600.021</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>600508.285</t>
+          <t>600508284510.784</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>506088.332</t>
+          <t>506088331843.893</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>498693.201</t>
+          <t>498693200902.056</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>535935.061</t>
+          <t>535935060943.867</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>85723.247</t>
+          <t>85723246749.221</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>91482.746</t>
+          <t>91482746168.0324</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>86195.415</t>
+          <t>86195414876.2805</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>59133.482</t>
+          <t>59133482025.1253</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>72841.853</t>
+          <t>72841852762.8707</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>87102.472</t>
+          <t>87102471751.0961</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>85987.16</t>
+          <t>85987159655.5743</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>95505.941</t>
+          <t>95505941007.3105</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>95189.869</t>
+          <t>95189869402.3999</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>102908.832</t>
+          <t>102908831977.756</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>114978.438</t>
+          <t>114978437743.571</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>121205.467</t>
+          <t>121205467148.358</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>112073.624</t>
+          <t>112073623505.956</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>90289.231</t>
+          <t>90289231417.0667</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>84821.844</t>
+          <t>84821843625.114</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>862.004</t>
+          <t>862003691.898881</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1069.918</t>
+          <t>1069918396.52735</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1352.167</t>
+          <t>1352166991.85402</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1713.361</t>
+          <t>1713361405.49617</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1709.084</t>
+          <t>1709084392.08655</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1712.617</t>
+          <t>1712617356.7307</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1810.461</t>
+          <t>1810460986.20763</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2084.662</t>
+          <t>2084661938.5762</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2406.598</t>
+          <t>2406597938.50795</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2899.066</t>
+          <t>2899066286.75236</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3150.366</t>
+          <t>3150366346.09588</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3552.429</t>
+          <t>3552428901.81319</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>3912.987</t>
+          <t>3912986646.28034</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>4381.356</t>
+          <t>4381356409.87214</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>3622.834</t>
+          <t>3622833878.53675</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3351.745</t>
+          <t>3351745111.42683</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3253.325</t>
+          <t>3253324819.21692</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3069.432</t>
+          <t>3069431907.57485</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>3394.137</t>
+          <t>3394136930.49287</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>3524.317</t>
+          <t>3524317120.56267</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3564.753</t>
+          <t>3564753044.57349</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3899.341</t>
+          <t>3899340652.87328</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>4272.915</t>
+          <t>4272914693.79163</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>4572.367</t>
+          <t>4572367290.08531</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>5134.014</t>
+          <t>5134013563.38492</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>5145.837</t>
+          <t>5145836634.70573</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>5135.711</t>
+          <t>5135710965.89013</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>5124.028</t>
+          <t>5124027749.67774</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>5626.101</t>
+          <t>5626100913.00537</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>5846.162</t>
+          <t>5846162461.80544</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>747.504</t>
+          <t>747504338.352453</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>875.478</t>
+          <t>875477883.751195</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>948.779</t>
+          <t>948778883.664245</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1079.544</t>
+          <t>1079544048.92964</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1152.602</t>
+          <t>1152601619.36337</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1228.308</t>
+          <t>1228307994.46433</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1286.632</t>
+          <t>1286632392.24568</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1363.681</t>
+          <t>1363680819.58956</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1461.974</t>
+          <t>1461973684.23098</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1726.338</t>
+          <t>1726337844.31475</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1989.305</t>
+          <t>1989304714.68435</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2405.866</t>
+          <t>2405866119.74867</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>3123.954</t>
+          <t>3123954460.27806</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>3522.095</t>
+          <t>3522095329.0551</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2606.169</t>
+          <t>2606168592.14996</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>33536.149</t>
+          <t>33536149278.2299</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>35092.741</t>
+          <t>35092741404.3735</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>44814.279</t>
+          <t>44814279036.1118</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>51821.689</t>
+          <t>51821688773.2249</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>59419.721</t>
+          <t>59419720923.6736</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>75419.557</t>
+          <t>75419556896.0452</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>86144.595</t>
+          <t>86144595058.0707</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>87586.024</t>
+          <t>87586023632.519</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>72671.102</t>
+          <t>72671101798.4128</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>71830.728</t>
+          <t>71830727985.5996</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>74301.423</t>
+          <t>74301422965.7421</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>74663.616</t>
+          <t>74663616053.4345</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>67242.685</t>
+          <t>67242684603.4815</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>63069.11</t>
+          <t>63069109799.6826</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>54240.672</t>
+          <t>54240672241.7022</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>556.1</t>
+          <t>556100296.141532</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>576.15</t>
+          <t>576149951.751794</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>575.748</t>
+          <t>575747934.400681</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>642.973</t>
+          <t>642973173.821213</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>648.345</t>
+          <t>648345474.426813</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>648.997</t>
+          <t>648997087.36027</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>702.041</t>
+          <t>702041333.566067</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>748.019</t>
+          <t>748019413.255718</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>773.818</t>
+          <t>773817638.838697</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>847.807</t>
+          <t>847806579.750752</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>808.549</t>
+          <t>808548851.090347</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>801.214</t>
+          <t>801214100.69862</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>771.759</t>
+          <t>771759245.883185</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>865.292</t>
+          <t>865291927.933365</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>862.057</t>
+          <t>862057058.816201</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>73668.333</t>
+          <t>73668332531.5688</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>71063.974</t>
+          <t>71063973633.8031</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>66860.805</t>
+          <t>66860805229.1568</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>75045.523</t>
+          <t>75045523448.6494</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>76357.561</t>
+          <t>76357560842.0014</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>74312.791</t>
+          <t>74312791125.0809</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>79609.89</t>
+          <t>79609890129.9766</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>86019.09</t>
+          <t>86019089618.2127</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>91890.811</t>
+          <t>91890811443.3972</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>99629.05</t>
+          <t>99629050149.7488</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>93935.475</t>
+          <t>93935475483.3943</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>91570.248</t>
+          <t>91570248200.5821</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>89015.04</t>
+          <t>89015039671.8551</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>89190.879</t>
+          <t>89190878732.0285</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>90703.727</t>
+          <t>90703726794.3642</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>19037.303</t>
+          <t>19037302514.1637</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>21575.944</t>
+          <t>21575944276.6626</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>22727.164</t>
+          <t>22727163577.1845</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>26615.048</t>
+          <t>26615048420.4627</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>25331.343</t>
+          <t>25331342514.0537</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>26214.921</t>
+          <t>26214921354.903</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30553.31</t>
+          <t>30553310451.9809</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>29564.769</t>
+          <t>29564768958.9844</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>27383.695</t>
+          <t>27383695223.3874</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>29327.337</t>
+          <t>29327337135.4935</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>32320.537</t>
+          <t>32320536983.8513</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>33433.882</t>
+          <t>33433881845.7211</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>35136.086</t>
+          <t>35136086001.8315</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>40967.319</t>
+          <t>40967318543.901</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>34476.76</t>
+          <t>34476760239.577</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>18760.369</t>
+          <t>18760369287.3413</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>19254.2</t>
+          <t>19254199897.0224</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19023.402</t>
+          <t>19023402006.0099</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>21388.731</t>
+          <t>21388730623.304</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>21761.231</t>
+          <t>21761231203.2949</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>21417.008</t>
+          <t>21417008017.6699</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>22540.288</t>
+          <t>22540287922.5308</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>24377.232</t>
+          <t>24377232104.7977</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>25968.749</t>
+          <t>25968749270.4443</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>28500.544</t>
+          <t>28500544066.203</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>27807.613</t>
+          <t>27807613443.5877</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>27662.597</t>
+          <t>27662597197.0255</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>26409.341</t>
+          <t>26409341145.4127</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>26016.54</t>
+          <t>26016539785.5522</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>26006.193</t>
+          <t>26006192576.9165</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4915.541</t>
+          <t>4915540619.09521</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4741.3</t>
+          <t>4741299899.56295</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>4036.68</t>
+          <t>4036680102.03402</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>5872.157</t>
+          <t>5872156675.60183</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4609.302</t>
+          <t>4609302240.76789</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>5670.027</t>
+          <t>5670027331.40868</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>6589.771</t>
+          <t>6589771040.96595</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>6935.9</t>
+          <t>6935900071.31536</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>7371.849</t>
+          <t>7371848697.41598</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>8953.334</t>
+          <t>8953334475.42843</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>11517.264</t>
+          <t>11517263811.2471</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>12975.237</t>
+          <t>12975237163.0891</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>15412.154</t>
+          <t>15412154076.8715</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>17770.119</t>
+          <t>17770118919.6354</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>14546.671</t>
+          <t>14546670710.5234</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>52016.337</t>
+          <t>52016336930.0046</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>62245.62</t>
+          <t>62245619616.4512</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>63873.496</t>
+          <t>63873496380.183</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>51566.752</t>
+          <t>51566752208.4561</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>29490.075</t>
+          <t>29490075260.8925</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>40138.691</t>
+          <t>40138691390.6187</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>49029.692</t>
+          <t>49029692268.2832</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>56269.507</t>
+          <t>56269506594.011</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>59463.905</t>
+          <t>59463904644.7534</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>76662.074</t>
+          <t>76662074316.3116</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>89673.01</t>
+          <t>89673009991.8763</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>107953.272</t>
+          <t>107953272404.597</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>121843.213</t>
+          <t>121843212642.434</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>138507.317</t>
+          <t>138507317347.76</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>110954.573</t>
+          <t>110954572811.513</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2028.31</t>
+          <t>2028309890.58239</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2217.855</t>
+          <t>2217854504.91107</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2430.998</t>
+          <t>2430997830.99864</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2675.83</t>
+          <t>2675829894.09672</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2318.37</t>
+          <t>2318369634.91021</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2434.539</t>
+          <t>2434539467.18296</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2515.165</t>
+          <t>2515165019.41571</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2833.433</t>
+          <t>2833432762.10264</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>3295.529</t>
+          <t>3295529331.06625</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>3849.11</t>
+          <t>3849109566.20234</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>4117.551</t>
+          <t>4117551350.04156</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>4420.813</t>
+          <t>4420812524.16568</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>4955.271</t>
+          <t>4955271016.55522</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>5635.399</t>
+          <t>5635399128.91328</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>5842.193</t>
+          <t>5842193182.92054</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>3998.683</t>
+          <t>3998682980.44458</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3823.393</t>
+          <t>3823392838.55434</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>3698.076</t>
+          <t>3698075797.20066</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>4062.367</t>
+          <t>4062366611.87639</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4059.05</t>
+          <t>4059049705.16391</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>3911.045</t>
+          <t>3911045073.77313</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>4153.632</t>
+          <t>4153632097.8479</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>4511.768</t>
+          <t>4511767687.9914</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>4902.071</t>
+          <t>4902070863.27676</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>5510</t>
+          <t>5510000138.13531</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>5412.287</t>
+          <t>5412286574.16123</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>5417.139</t>
+          <t>5417138545.76695</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>5465.737</t>
+          <t>5465737275.99107</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>5730.681</t>
+          <t>5730681450.92897</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>5707.363</t>
+          <t>5707362825.92864</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>45811.492</t>
+          <t>45811491641.2324</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>50548.802</t>
+          <t>50548802300.6007</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>47240.819</t>
+          <t>47240818540.3917</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>50226.033</t>
+          <t>50226032551.9244</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>49500.97</t>
+          <t>49500970286.5531</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>51624.774</t>
+          <t>51624774345.5517</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>50286.607</t>
+          <t>50286606929.0418</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>53688.773</t>
+          <t>53688773463.1632</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>57740.028</t>
+          <t>57740027697.9751</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>63176.404</t>
+          <t>63176403572.9896</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>59814.253</t>
+          <t>59814252904.9033</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>58246.824</t>
+          <t>58246824414.7556</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>57596.73</t>
+          <t>57596729639.1113</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>54019.377</t>
+          <t>54019377037.594</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>48239.872</t>
+          <t>48239871968.4856</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>16091.758</t>
+          <t>16091757551.0401</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>18594.97</t>
+          <t>18594970408.1419</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>21755</t>
+          <t>21755000031.538</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>23566.758</t>
+          <t>23566758187.9793</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>26618.861</t>
+          <t>26618861144.5638</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>27814.643</t>
+          <t>27814643171.7851</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>21017.764</t>
+          <t>21017763664.313</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>20530.861</t>
+          <t>20530860674.453</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>22981.975</t>
+          <t>22981974912.8432</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>28444.649</t>
+          <t>28444649218.094</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>33058.449</t>
+          <t>33058449297.4461</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>33372.473</t>
+          <t>33372473424.1058</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>34742.811</t>
+          <t>34742811093.5155</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>35163.122</t>
+          <t>35163122490.7306</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>31050.715</t>
+          <t>31050714545.7707</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>47927.41</t>
+          <t>47927410264.3208</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>49163.401</t>
+          <t>49163400737.1816</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>51735.379</t>
+          <t>51735378629.4081</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>49321.914</t>
+          <t>49321914202.3783</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>52199.606</t>
+          <t>52199606206.5527</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>58701.663</t>
+          <t>58701663447.6273</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>55279.974</t>
+          <t>55279974200.1822</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>52542.155</t>
+          <t>52542155368.6365</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>47079.977</t>
+          <t>47079976795.5178</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>48534.129</t>
+          <t>48534129182.9959</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>49178.928</t>
+          <t>49178927959.0077</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>47362.015</t>
+          <t>47362015221.7089</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>40732.2</t>
+          <t>40732200374.4137</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>37770.408</t>
+          <t>37770408384.744</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>36781.227</t>
+          <t>36781227251.936</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1414757.06</t>
+          <t>1414757059942.76</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1450646.717</t>
+          <t>1450646717135.85</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1584855.368</t>
+          <t>1584855367704.28</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1798882.203</t>
+          <t>1798882202802.67</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1892973.88</t>
+          <t>1892973880389.25</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2141082.839</t>
+          <t>2141082839279.63</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2285188.931</t>
+          <t>2285188930524.43</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2281881.211</t>
+          <t>2281881211359.17</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2069134.948</t>
+          <t>2069134948318.46</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2097793.391</t>
+          <t>2097793391215.15</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2062672.209</t>
+          <t>2062672209253.71</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2024514.302</t>
+          <t>2024514302484.16</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>1799028.276</t>
+          <t>1799028276001.56</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>1639714.428</t>
+          <t>1639714427779.11</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>1684265.582</t>
+          <t>1684265581819.62</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>569891.563</t>
+          <t>569891562637.698</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>588528.746</t>
+          <t>588528746228.932</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>613115.739</t>
+          <t>613115738950.916</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>626992.811</t>
+          <t>626992811022.518</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>627758.234</t>
+          <t>627758233635.901</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>686943.163</t>
+          <t>686943163171.864</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>705756.698</t>
+          <t>705756698037.94</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>676708.637</t>
+          <t>676708636756.705</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>651218.738</t>
+          <t>651218738482.546</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>723924.131</t>
+          <t>723924130739.99</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>773797.347</t>
+          <t>773797347240.803</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>819015.5</t>
+          <t>819015500030.575</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>802252.008</t>
+          <t>802252007539.003</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>869183.765</t>
+          <t>869183764583.244</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>857862.773</t>
+          <t>857862773465.988</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>5237932.273</t>
+          <t>5237932272614.18</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5181841.682</t>
+          <t>5181841681850.12</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5289611.072</t>
+          <t>5289611072356.04</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>5619110.407</t>
+          <t>5619110407186.35</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>5772370.565</t>
+          <t>5772370564586.16</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>6243251.115</t>
+          <t>6243251114855.93</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6417216.163</t>
+          <t>6417216163462.55</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>6455165.927</t>
+          <t>6455165926962.1</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>6232437.765</t>
+          <t>6232437764571.92</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>6665927.391</t>
+          <t>6665927391413.35</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>6641954.498</t>
+          <t>6641954497659.22</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>6628312.97</t>
+          <t>6628312969965.3</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>6236811.519</t>
+          <t>6236811519288.86</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>6123104.895</t>
+          <t>6123104894562.19</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>6178263.432</t>
+          <t>6178263431506.05</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>labour_force_value.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
